--- a/Design Files/Industrial IOT development board-v1.0/BOM/Client-BOM-v1.0.xlsx
+++ b/Design Files/Industrial IOT development board-v1.0/BOM/Client-BOM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="699">
   <si>
     <t>#</t>
   </si>
@@ -1092,9 +1092,6 @@
     <t>Cap-0402</t>
   </si>
   <si>
-    <t>UCD-220uF-10mmDia</t>
-  </si>
-  <si>
     <t>RVT1H470M0607</t>
   </si>
   <si>
@@ -1125,9 +1122,6 @@
     <t>Case-E</t>
   </si>
   <si>
-    <t>EEEFK1J220P</t>
-  </si>
-  <si>
     <t>SMB_</t>
   </si>
   <si>
@@ -1176,9 +1170,6 @@
     <t>U263-163N-4BQC65</t>
   </si>
   <si>
-    <t>Voltlink Target</t>
-  </si>
-  <si>
     <t>HDR1X4 Female</t>
   </si>
   <si>
@@ -1215,9 +1206,6 @@
     <t>XFL4020-102MEC</t>
   </si>
   <si>
-    <t>YSPI0520-2R2M_</t>
-  </si>
-  <si>
     <t>FCH1365-680M</t>
   </si>
   <si>
@@ -2098,13 +2086,43 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>2.54mm Pitch FC-6 JTAG ISP AVR Download Cable Wire Line 6P 6pin 30CM 300mm Connector Gray Flat Ribbon Data Cable 28AWG</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Cable (x1)</t>
+  </si>
+  <si>
+    <t>Coin Cell (x1)</t>
+  </si>
+  <si>
+    <t>CR2032 3V Lithium Battery DL2032 BR2032 5004LC 2032 for watch, toys, car key, Calculator +screwdrive</t>
+  </si>
+  <si>
+    <t>1.3 Inch OLED Display Module 128X64 LCD Display 4PIN I2C IIC Communicate For Arduino</t>
+  </si>
+  <si>
+    <t>3.7V 3500mah 18650 Battery For Samsung 35E INR 18650 20A Lithium Lon Battery Replacement External Battery+Charger</t>
+  </si>
+  <si>
+    <t>18650 battery (x1) - This one is used cell category... New and original not available</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2159,6 +2177,22 @@
       <b/>
       <strike/>
       <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2277,10 +2311,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2317,9 +2352,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2329,8 +2361,21 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2616,7 +2661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:L164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2640,9 +2685,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2662,19 +2707,19 @@
         <v>355</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2696,13 +2741,13 @@
         <v>356</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J3" s="7">
         <v>19</v>
@@ -2712,7 +2757,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B160" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B162" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -2725,16 +2770,16 @@
         <v>200</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>357</v>
+        <v>689</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
@@ -2756,17 +2801,17 @@
       <c r="E5" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>358</v>
+      <c r="F5" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J5" s="7">
         <v>1</v>
@@ -2789,16 +2834,16 @@
         <v>202</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
@@ -2821,16 +2866,16 @@
         <v>203</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="J7" s="7">
         <v>7</v>
@@ -2853,16 +2898,16 @@
         <v>204</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="J8" s="9">
         <v>4</v>
@@ -2885,16 +2930,16 @@
         <v>205</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
@@ -2917,16 +2962,16 @@
         <v>206</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>362</v>
+        <v>689</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -2949,16 +2994,16 @@
         <v>207</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="J11" s="7">
         <v>6</v>
@@ -2981,16 +3026,16 @@
         <v>208</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J12" s="9">
         <v>1</v>
@@ -3013,16 +3058,16 @@
         <v>209</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -3045,16 +3090,16 @@
         <v>210</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -3077,16 +3122,16 @@
         <v>211</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J15" s="7">
         <v>2</v>
@@ -3109,16 +3154,16 @@
         <v>212</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>364</v>
+        <v>689</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="J16" s="9">
         <v>2</v>
@@ -3144,13 +3189,13 @@
         <v>356</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="J17" s="7">
         <v>2</v>
@@ -3173,16 +3218,16 @@
         <v>214</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>365</v>
+        <v>689</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -3208,13 +3253,13 @@
         <v>356</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -3230,29 +3275,29 @@
       <c r="C20" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="J20" s="15">
-        <v>1</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>691</v>
+      <c r="G20" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="J20" s="14">
+        <v>1</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3271,16 +3316,16 @@
         <v>216</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -3303,16 +3348,16 @@
         <v>217</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="J22" s="9">
         <v>2</v>
@@ -3335,16 +3380,16 @@
         <v>218</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="J23" s="7">
         <v>2</v>
@@ -3367,21 +3412,21 @@
         <v>219</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="J24" s="9">
         <v>1</v>
       </c>
-      <c r="K24" s="17"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -3399,16 +3444,16 @@
         <v>220</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="J25" s="7">
         <v>2</v>
@@ -3431,16 +3476,16 @@
         <v>221</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="J26" s="9">
         <v>4</v>
@@ -3463,16 +3508,16 @@
         <v>222</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -3498,13 +3543,13 @@
         <v>356</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="J28" s="9">
         <v>2</v>
@@ -3527,16 +3572,16 @@
         <v>224</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -3559,16 +3604,16 @@
         <v>225</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="J30" s="9">
         <v>3</v>
@@ -3591,16 +3636,16 @@
         <v>226</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="J31" s="7">
         <v>2</v>
@@ -3623,16 +3668,16 @@
         <v>227</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>366</v>
+        <v>689</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="J32" s="9">
         <v>1</v>
@@ -3658,13 +3703,13 @@
         <v>356</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -3690,13 +3735,13 @@
         <v>356</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="J34" s="9">
         <v>1</v>
@@ -3719,16 +3764,16 @@
         <v>230</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="J35" s="7">
         <v>1</v>
@@ -3751,16 +3796,16 @@
         <v>231</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="J36" s="9">
         <v>1</v>
@@ -3776,29 +3821,29 @@
       <c r="C37" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="F37" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="J37" s="15">
+      <c r="F37" s="14" t="s">
+        <v>360</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="J37" s="14">
         <v>2</v>
       </c>
-      <c r="K37" s="17" t="s">
-        <v>691</v>
+      <c r="K37" s="16" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3817,16 +3862,16 @@
         <v>233</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>368</v>
+        <v>689</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="J38" s="9">
         <v>1</v>
@@ -3849,16 +3894,16 @@
         <v>234</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J39" s="7">
         <v>1</v>
@@ -3881,16 +3926,16 @@
         <v>235</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J40" s="9">
         <v>9</v>
@@ -3913,16 +3958,16 @@
         <v>236</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J41" s="7">
         <v>1</v>
@@ -3945,16 +3990,16 @@
         <v>237</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J42" s="9">
         <v>1</v>
@@ -3977,16 +4022,16 @@
         <v>238</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J43" s="7">
         <v>1</v>
@@ -4009,16 +4054,16 @@
         <v>239</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
@@ -4041,16 +4086,16 @@
         <v>240</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
@@ -4073,16 +4118,16 @@
         <v>241</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J46" s="9">
         <v>1</v>
@@ -4105,16 +4150,16 @@
         <v>242</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J47" s="7">
         <v>12</v>
@@ -4137,16 +4182,16 @@
         <v>243</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J48" s="9">
         <v>8</v>
@@ -4169,16 +4214,16 @@
         <v>244</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J49" s="7">
         <v>4</v>
@@ -4201,16 +4246,16 @@
         <v>245</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J50" s="9">
         <v>4</v>
@@ -4233,16 +4278,16 @@
         <v>246</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J51" s="7">
         <v>1</v>
@@ -4265,16 +4310,16 @@
         <v>247</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J52" s="9">
         <v>2</v>
@@ -4297,16 +4342,16 @@
         <v>248</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J53" s="7">
         <v>1</v>
@@ -4329,16 +4374,16 @@
         <v>249</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
@@ -4361,16 +4406,16 @@
         <v>250</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J55" s="7">
         <v>1</v>
@@ -4393,16 +4438,16 @@
         <v>251</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J56" s="9">
         <v>2</v>
@@ -4425,16 +4470,16 @@
         <v>252</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J57" s="7">
         <v>2</v>
@@ -4457,16 +4502,16 @@
         <v>253</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J58" s="9">
         <v>2</v>
@@ -4489,16 +4534,16 @@
         <v>254</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -4521,16 +4566,16 @@
         <v>255</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J60" s="9">
         <v>1</v>
@@ -4553,16 +4598,16 @@
         <v>256</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J61" s="7">
         <v>2</v>
@@ -4585,16 +4630,16 @@
         <v>257</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J62" s="9">
         <v>2</v>
@@ -4616,17 +4661,17 @@
       <c r="E63" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="F63" s="7" t="s">
-        <v>383</v>
+      <c r="F63" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J63" s="7">
         <v>9</v>
@@ -4649,16 +4694,16 @@
         <v>259</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>384</v>
+        <v>689</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J64" s="9">
         <v>1</v>
@@ -4680,17 +4725,17 @@
       <c r="E65" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>385</v>
+      <c r="F65" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J65" s="7">
         <v>1</v>
@@ -4713,16 +4758,16 @@
         <v>261</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J66" s="9">
         <v>1</v>
@@ -4744,17 +4789,17 @@
       <c r="E67" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>387</v>
+      <c r="F67" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J67" s="7">
         <v>1</v>
@@ -4777,16 +4822,16 @@
         <v>263</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>388</v>
+        <v>689</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J68" s="9">
         <v>2</v>
@@ -4808,17 +4853,17 @@
       <c r="E69" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>389</v>
+      <c r="F69" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J69" s="7">
         <v>1</v>
@@ -4841,16 +4886,16 @@
         <v>265</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>390</v>
+        <v>689</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J70" s="9">
         <v>3</v>
@@ -4872,17 +4917,17 @@
       <c r="E71" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>391</v>
+      <c r="F71" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J71" s="7">
         <v>1</v>
@@ -4905,16 +4950,16 @@
         <v>267</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>392</v>
+        <v>689</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J72" s="9">
         <v>1</v>
@@ -4936,17 +4981,17 @@
       <c r="E73" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>393</v>
+      <c r="F73" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J73" s="7">
         <v>1</v>
@@ -4969,16 +5014,16 @@
         <v>269</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J74" s="9">
         <v>1</v>
@@ -5000,17 +5045,17 @@
       <c r="E75" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>395</v>
+      <c r="F75" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J75" s="7">
         <v>4</v>
@@ -5033,16 +5078,16 @@
         <v>271</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>396</v>
+        <v>689</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="J76" s="9">
         <v>1</v>
@@ -5064,17 +5109,17 @@
       <c r="E77" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>397</v>
+      <c r="F77" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="J77" s="7">
         <v>1</v>
@@ -5097,16 +5142,16 @@
         <v>273</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>398</v>
+        <v>689</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="J78" s="9">
         <v>1</v>
@@ -5128,17 +5173,17 @@
       <c r="E79" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>399</v>
+      <c r="F79" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="J79" s="7">
         <v>1</v>
@@ -5161,16 +5206,16 @@
         <v>275</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J80" s="9">
         <v>5</v>
@@ -5192,17 +5237,17 @@
       <c r="E81" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>401</v>
+      <c r="F81" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J81" s="7">
         <v>1</v>
@@ -5225,16 +5270,16 @@
         <v>277</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J82" s="9">
         <v>6</v>
@@ -5257,16 +5302,16 @@
         <v>278</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J83" s="7">
         <v>1</v>
@@ -5289,16 +5334,16 @@
         <v>279</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J84" s="9">
         <v>1</v>
@@ -5321,16 +5366,16 @@
         <v>280</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J85" s="7">
         <v>5</v>
@@ -5353,16 +5398,16 @@
         <v>281</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J86" s="9">
         <v>1</v>
@@ -5385,16 +5430,16 @@
         <v>282</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="J87" s="7">
         <v>1</v>
@@ -5417,16 +5462,16 @@
         <v>283</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G88" s="10" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="J88" s="9">
         <v>1</v>
@@ -5449,16 +5494,16 @@
         <v>284</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J89" s="7">
         <v>1</v>
@@ -5481,16 +5526,16 @@
         <v>285</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J90" s="9">
         <v>2</v>
@@ -5513,16 +5558,16 @@
         <v>286</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="J91" s="7">
         <v>1</v>
@@ -5545,16 +5590,16 @@
         <v>287</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="J92" s="9">
         <v>2</v>
@@ -5577,16 +5622,16 @@
         <v>288</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="J93" s="7">
         <v>1</v>
@@ -5609,16 +5654,16 @@
         <v>289</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="J94" s="9">
         <v>2</v>
@@ -5641,16 +5686,16 @@
         <v>290</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="J95" s="7">
         <v>23</v>
@@ -5673,16 +5718,16 @@
         <v>291</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J96" s="9">
         <v>2</v>
@@ -5705,16 +5750,16 @@
         <v>292</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="J97" s="7">
         <v>1</v>
@@ -5737,16 +5782,16 @@
         <v>293</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="J98" s="9">
         <v>2</v>
@@ -5769,16 +5814,16 @@
         <v>294</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="J99" s="7">
         <v>1</v>
@@ -5801,16 +5846,16 @@
         <v>295</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J100" s="9">
         <v>1</v>
@@ -5833,16 +5878,16 @@
         <v>296</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="J101" s="7">
         <v>2</v>
@@ -5865,16 +5910,16 @@
         <v>297</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I102" s="10" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J102" s="9">
         <v>9</v>
@@ -5897,16 +5942,16 @@
         <v>298</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="J103" s="7">
         <v>3</v>
@@ -5922,29 +5967,29 @@
       <c r="C104" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D104" s="15" t="s">
+      <c r="D104" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E104" s="16" t="s">
+      <c r="E104" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F104" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="G104" s="16" t="s">
-        <v>501</v>
-      </c>
-      <c r="H104" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="I104" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="J104" s="15">
+      <c r="F104" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="I104" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="J104" s="14">
         <v>2</v>
       </c>
-      <c r="K104" s="17" t="s">
-        <v>691</v>
+      <c r="K104" s="16" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5963,16 +6008,16 @@
         <v>299</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="J105" s="7">
         <v>5</v>
@@ -5995,16 +6040,16 @@
         <v>300</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J106" s="9">
         <v>5</v>
@@ -6027,16 +6072,16 @@
         <v>301</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J107" s="7">
         <v>7</v>
@@ -6059,16 +6104,16 @@
         <v>302</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="J108" s="9">
         <v>1</v>
@@ -6091,16 +6136,16 @@
         <v>303</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="J109" s="7">
         <v>1</v>
@@ -6123,16 +6168,16 @@
         <v>304</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G110" s="10" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I110" s="10" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="J110" s="9">
         <v>5</v>
@@ -6155,16 +6200,16 @@
         <v>305</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="J111" s="7">
         <v>8</v>
@@ -6187,16 +6232,16 @@
         <v>306</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="J112" s="9">
         <v>4</v>
@@ -6219,16 +6264,16 @@
         <v>307</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="J113" s="7">
         <v>4</v>
@@ -6251,16 +6296,16 @@
         <v>308</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="H114" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I114" s="10" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="J114" s="9">
         <v>2</v>
@@ -6283,16 +6328,16 @@
         <v>309</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="J115" s="7">
         <v>3</v>
@@ -6315,16 +6360,16 @@
         <v>310</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G116" s="10" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H116" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I116" s="10" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="J116" s="9">
         <v>4</v>
@@ -6347,16 +6392,16 @@
         <v>311</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="J117" s="7">
         <v>6</v>
@@ -6379,16 +6424,16 @@
         <v>312</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G118" s="10" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H118" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I118" s="10" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="J118" s="9">
         <v>2</v>
@@ -6411,16 +6456,16 @@
         <v>313</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="J119" s="7">
         <v>1</v>
@@ -6443,16 +6488,16 @@
         <v>314</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G120" s="10" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I120" s="10" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="J120" s="9">
         <v>1</v>
@@ -6475,16 +6520,16 @@
         <v>315</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="J121" s="7">
         <v>2</v>
@@ -6507,16 +6552,16 @@
         <v>316</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G122" s="10" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H122" s="9" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="I122" s="10" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="J122" s="9">
         <v>1</v>
@@ -6539,16 +6584,16 @@
         <v>317</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J123" s="7">
         <v>1</v>
@@ -6571,16 +6616,16 @@
         <v>318</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G124" s="10" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="I124" s="10" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="J124" s="9">
         <v>1</v>
@@ -6603,16 +6648,16 @@
         <v>319</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J125" s="7">
         <v>1</v>
@@ -6635,16 +6680,16 @@
         <v>320</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I126" s="10" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="J126" s="9">
         <v>1</v>
@@ -6667,16 +6712,16 @@
         <v>321</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="J127" s="7">
         <v>1</v>
@@ -6699,16 +6744,16 @@
         <v>322</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G128" s="10" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="J128" s="9">
         <v>2</v>
@@ -6731,16 +6776,16 @@
         <v>323</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J129" s="7">
         <v>1</v>
@@ -6763,16 +6808,16 @@
         <v>324</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G130" s="10" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="J130" s="9">
         <v>1</v>
@@ -6795,16 +6840,16 @@
         <v>325</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="J131" s="7">
         <v>1</v>
@@ -6827,16 +6872,16 @@
         <v>326</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G132" s="10" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="J132" s="9">
         <v>1</v>
@@ -6852,29 +6897,29 @@
       <c r="C133" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E133" s="16" t="s">
+      <c r="E133" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="F133" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="G133" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="H133" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="I133" s="16" t="s">
-        <v>634</v>
-      </c>
-      <c r="J133" s="15">
+      <c r="F133" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="G133" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="H133" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="I133" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="J133" s="14">
         <v>2</v>
       </c>
-      <c r="K133" s="17" t="s">
-        <v>691</v>
+      <c r="K133" s="16" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -6893,16 +6938,16 @@
         <v>328</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>412</v>
+        <v>689</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="J134" s="9">
         <v>3</v>
@@ -6924,17 +6969,17 @@
       <c r="E135" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>413</v>
+      <c r="F135" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H135" s="7" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J135" s="7">
         <v>1</v>
@@ -6957,16 +7002,16 @@
         <v>330</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>414</v>
+        <v>689</v>
       </c>
       <c r="G136" s="10" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J136" s="9">
         <v>2</v>
@@ -6988,17 +7033,17 @@
       <c r="E137" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>415</v>
+      <c r="F137" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J137" s="7">
         <v>2</v>
@@ -7021,16 +7066,16 @@
         <v>332</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>416</v>
+        <v>689</v>
       </c>
       <c r="G138" s="10" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J138" s="9">
         <v>1</v>
@@ -7052,17 +7097,17 @@
       <c r="E139" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="F139" s="7" t="s">
-        <v>417</v>
+      <c r="F139" s="9" t="s">
+        <v>689</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J139" s="7">
         <v>1</v>
@@ -7085,16 +7130,16 @@
         <v>334</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>418</v>
+        <v>689</v>
       </c>
       <c r="G140" s="10" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J140" s="9">
         <v>1</v>
@@ -7117,16 +7162,16 @@
         <v>335</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J141" s="7">
         <v>1</v>
@@ -7149,16 +7194,16 @@
         <v>336</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G142" s="10" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="H142" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J142" s="9">
         <v>1</v>
@@ -7181,16 +7226,16 @@
         <v>337</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J143" s="7">
         <v>1</v>
@@ -7213,16 +7258,16 @@
         <v>338</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G144" s="10" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="H144" s="9" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J144" s="9">
         <v>1</v>
@@ -7245,16 +7290,16 @@
         <v>339</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J145" s="7">
         <v>1</v>
@@ -7277,16 +7322,16 @@
         <v>340</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G146" s="10" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="H146" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J146" s="9">
         <v>2</v>
@@ -7309,16 +7354,16 @@
         <v>341</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J147" s="7">
         <v>1</v>
@@ -7341,16 +7386,16 @@
         <v>342</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G148" s="10" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="H148" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I148" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J148" s="9">
         <v>1</v>
@@ -7373,16 +7418,16 @@
         <v>343</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J149" s="7">
         <v>1</v>
@@ -7405,16 +7450,16 @@
         <v>344</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G150" s="10" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="H150" s="9" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J150" s="9">
         <v>1</v>
@@ -7437,16 +7482,16 @@
         <v>345</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="I151" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J151" s="7">
         <v>1</v>
@@ -7469,16 +7514,16 @@
         <v>346</v>
       </c>
       <c r="F152" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="G152" s="10" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H152" s="9" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="I152" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J152" s="9">
         <v>8</v>
@@ -7501,16 +7546,16 @@
         <v>347</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I153" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J153" s="7">
         <v>1</v>
@@ -7533,16 +7578,16 @@
         <v>348</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="G154" s="10" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="H154" s="9" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="I154" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J154" s="9">
         <v>1</v>
@@ -7565,16 +7610,16 @@
         <v>349</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="I155" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J155" s="7">
         <v>1</v>
@@ -7597,16 +7642,16 @@
         <v>350</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G156" s="10" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="H156" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I156" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J156" s="9">
         <v>1</v>
@@ -7629,16 +7674,16 @@
         <v>351</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I157" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J157" s="7">
         <v>1</v>
@@ -7661,16 +7706,16 @@
         <v>352</v>
       </c>
       <c r="F158" s="9" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G158" s="10" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="H158" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="I158" s="8" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="J158" s="9">
         <v>1</v>
@@ -7693,16 +7738,16 @@
         <v>353</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="H159" s="7" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="I159" s="8" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="J159" s="7">
         <v>1</v>
@@ -7725,27 +7770,168 @@
         <v>354</v>
       </c>
       <c r="F160" s="9" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="G160" s="10" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="H160" s="9" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="I160" s="10" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="J160" s="9">
         <v>1</v>
       </c>
       <c r="K160" s="9"/>
+    </row>
+    <row r="161" spans="2:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B161" s="11">
+        <f>ROW(B161) - ROW($B$2)</f>
+        <v>159</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="E161" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="K161" s="18" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="162" spans="2:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B162" s="11">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="E162" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J162" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="K162" s="19" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="163" spans="2:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="11">
+        <f>ROW(B163) - ROW($B$2)</f>
+        <v>161</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="E163" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J163" s="7">
+        <v>1</v>
+      </c>
+      <c r="K163" s="18" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="164" spans="2:12" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B164" s="11">
+        <f t="shared" ref="B164" si="1">ROW(B164) - ROW($B$2)</f>
+        <v>162</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J164" s="9">
+        <v>1</v>
+      </c>
+      <c r="K164" s="19" t="s">
+        <v>692</v>
+      </c>
+      <c r="L164" s="20" t="s">
+        <v>698</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K161" r:id="rId1"/>
+    <hyperlink ref="K162" r:id="rId2"/>
+    <hyperlink ref="K163" r:id="rId3"/>
+    <hyperlink ref="K164" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/Design Files/Industrial IOT development board-v1.0/BOM/Client-BOM-v1.0.xlsx
+++ b/Design Files/Industrial IOT development board-v1.0/BOM/Client-BOM-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1163" uniqueCount="701">
   <si>
     <t>#</t>
   </si>
@@ -2116,6 +2116,12 @@
   </si>
   <si>
     <t>18650 battery (x1) - This one is used cell category... New and original not available</t>
+  </si>
+  <si>
+    <t>Omada</t>
+  </si>
+  <si>
+    <t>POE160S</t>
   </si>
 </sst>
 </file>
@@ -2361,9 +2367,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2372,6 +2375,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2661,7 +2667,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L165"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2685,9 +2691,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -7815,7 +7821,7 @@
       <c r="J161" s="7" t="s">
         <v>693</v>
       </c>
-      <c r="K161" s="18" t="s">
+      <c r="K161" s="17" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7848,7 +7854,7 @@
       <c r="J162" s="9" t="s">
         <v>694</v>
       </c>
-      <c r="K162" s="19" t="s">
+      <c r="K162" s="18" t="s">
         <v>692</v>
       </c>
     </row>
@@ -7881,13 +7887,13 @@
       <c r="J163" s="7">
         <v>1</v>
       </c>
-      <c r="K163" s="18" t="s">
+      <c r="K163" s="17" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="164" spans="2:12" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B164" s="11">
-        <f t="shared" ref="B164" si="1">ROW(B164) - ROW($B$2)</f>
+        <f t="shared" ref="B164:B165" si="1">ROW(B164) - ROW($B$2)</f>
         <v>162</v>
       </c>
       <c r="C164" s="12" t="s">
@@ -7914,11 +7920,44 @@
       <c r="J164" s="9">
         <v>1</v>
       </c>
-      <c r="K164" s="19" t="s">
+      <c r="K164" s="18" t="s">
         <v>692</v>
       </c>
-      <c r="L164" s="20" t="s">
+      <c r="L164" s="19" t="s">
         <v>698</v>
+      </c>
+    </row>
+    <row r="165" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="11">
+        <f t="shared" si="1"/>
+        <v>163</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="E165" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J165" s="9">
+        <v>1</v>
+      </c>
+      <c r="K165" s="18" t="s">
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -7930,8 +7969,9 @@
     <hyperlink ref="K162" r:id="rId2"/>
     <hyperlink ref="K163" r:id="rId3"/>
     <hyperlink ref="K164" r:id="rId4"/>
+    <hyperlink ref="K165" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>